--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - Sr. Consultant level - DevOps</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ca6064f69a534e</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
@@ -853,35 +853,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analyst, Risk Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,137 +2806,137 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator) Hybrid - Washington, DC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tyndale Company</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pipersville, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, ECS, Spark, PySpark, CI/CD, GitHub Actions, Terraform, AKS</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e10d417269b254f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe4f28e6a73ade8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3422,11 +3422,11 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,29 +3566,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Infrastructure Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, SQL Server, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b90009cba8c2c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,17 +4371,227 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Scientist</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,52 +748,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IAM Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>IAM Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator) Hybrid - Washington, DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe4f28e6a73ade8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,19 +3681,19 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4345,251 +4345,6 @@
         </is>
       </c>
       <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Modeler</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Union Bank &amp; Trust Co.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Database Engineer III</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,50 +4301,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, YARN, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b946e93ff6faed4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Data Platform Engineer-4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ed45f65d56706e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Database Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4acce1067bbdaf41</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3492,11 +3492,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Teradata Developer-1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1dca4a550ee320</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,15 +4301,225 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SENIOR JAVA DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TransCore</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Modeler</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Union Bank &amp; Trust Co.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Scientist</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -888,35 +888,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,24 +976,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, YARN, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b946e93ff6faed4</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-4</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ed45f65d56706e</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Database Engineer III</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acce1067bbdaf41</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
+          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Teradata Developer-1</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1dca4a550ee320</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4450,76 +4450,6 @@
         </is>
       </c>
       <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud ETL Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ae806cfdce5e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=61076be5c1091dff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud ETL Software Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ae806cfdce5e5c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
@@ -783,52 +783,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ee673d162f6b2ce0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IAM Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>IAM Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>EDP Cloud Data Platform Administrator - US Citizen or Green Card</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Washon MedData Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=217b9f59d954e67c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Database Engineer III</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7df43db58f637436</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=30c536ee1ba37c5d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Python Full Stack Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, Spark, Scala, Kafka, Oracle, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=57d547726eb0c06b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,19 +3856,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
@@ -4452,6 +4452,76 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Celebration, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ece4794b980b0cdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Heartland Veterinary Partners</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ae96e01998eff74</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=924e4d3af2c44fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf8c642c375c95b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Backend (Cloud Architecture, Workflow Automation &amp; Systems Integration)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Metropolitan Transportation Authority</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>26.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61076be5c1091dff</t>
+          <t>https://www.indeed.com/viewjob?jk=924e4d3af2c44fbe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud ETL Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Alter Domus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ae806cfdce5e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=61076be5c1091dff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Databricks, BigQuery</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee673d162f6b2ce0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,94 +881,94 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IAM Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EDP Cloud Data Platform Administrator - US Citizen or Green Card</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Washon MedData Inc</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=217b9f59d954e67c</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,89 +1966,89 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,137 +2911,137 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c536ee1ba37c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Python Full Stack Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Spark, Scala, Kafka, Oracle, CI/CD, Python</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d547726eb0c06b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,602 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>API Developer - Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior QA Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Crisis Text Line</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Back-End Java Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Junior Dev Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>BlueVoyant</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>SENIOR JAVA DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>TransCore</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Modeler</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Union Bank &amp; Trust Co.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ece4794b980b0cdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Visualization Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Heartland Veterinary Partners</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae96e01998eff74</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
@@ -3925,6 +3925,41 @@
         </is>
       </c>
       <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alter Domus</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS, Databricks</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61076be5c1091dff</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
@@ -3925,41 +3925,6 @@
         </is>
       </c>
       <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3820,111 +3820,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
@@ -3820,6 +3820,41 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,46 +2652,46 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,182 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>SENIOR JAVA DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>TransCore</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Modeler</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Union Bank &amp; Trust Co.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,647 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DLA Piper</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Warehouse ETL Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Conduent</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Celebration, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>API Developer - Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior QA Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Crisis Text Line</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Back-End Java Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BRMi</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Junior Dev Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BlueVoyant</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SENIOR JAVA DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TransCore</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ops Solution Developer II</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer II</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>The Friedkin Group</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>The University of Michigan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,94 +811,94 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IAM Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ff466153d7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, Vertex AI, ETL, Terraform</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,682 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>API Security Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>DLA Piper</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Kubernetes Security Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>API Developer - Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior QA Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Crisis Text Line</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=921045e38c294529</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Back-End Java Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Junior Dev Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>BlueVoyant</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>SENIOR JAVA DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>TransCore</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>The University of Michigan</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>PROJITT LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -841,29 +841,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer Remote</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,190 +3461,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,42 +748,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -806,12 +806,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SiriusPoint</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,85 +3391,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>PROJITT LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PROJITT LLC</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d647606f8497de</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Herzing University</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Only local to California, W2, GC and USC )</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24670d848e01b14</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb094f55a98987f</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, DataOps, Git</t>
+          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,295 +3111,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>SENIOR JAVA DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>United States Cold Storage</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Camden, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>TransCore</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c50af91cfa81599</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Architect (Distributed Systems Engineering)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,147 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PROJITT LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,52 +556,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>PROJITT LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,49 +671,49 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -736,29 +736,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes (USC/GC/OPT) W2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7356480f3cd54878</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>SUPPLIER.IO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Compute Platform Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect (Distributed Systems Engineering)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bad59177479f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2840,146 +2840,6 @@
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>The Friedkin Group</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
         </is>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PROJITT LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>PROJITT LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Backend Engineer, Core APIsNew</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FINGERPRINT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
         </is>
       </c>
     </row>
@@ -1378,25 +1378,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2- PostgreSQL and Oracle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52112fe5f20617f</t>
+          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fd49668a3407ae</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Sr. Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>American Medical Association (AMA)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning / Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Vector Resources, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
+          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Collegeville, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Compute Platform Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
+          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ops Solution Developer II</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Modeling, ETL, ELT, Power BI, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,112 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a54459f220be02d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Junior Dev Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BlueVoyant</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ops Solution Developer II</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-07.xlsx
+++ b/results/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Cloud Architecture, Workflow Automation &amp; Systems Integration)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Metropolitan Transportation Authority</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.4</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=924e4d3af2c44fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9178b9a80d2d5100</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PROJITT LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>PartnerCo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Scala, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -771,29 +771,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer- Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0545991ebbdd6454</t>
+          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PartnerCo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f130792df2134b12</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Advisory Full Stack Engineer, AI Orchestration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - LLMOps &amp; MLOps</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, MySQL, Splunk, MLOps, CI/CD</t>
+          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
+          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MLOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd8d51c031cacc</t>
+          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Core APIsNew</t>
+          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FINGERPRINT</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c5fd6afaad69e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526767881c72befd</t>
+          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896e1523c301ce2f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88577baa482b8f47</t>
+          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CloudOps Engineer – Platform Engineering (EKS)</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c68f9b0d2e63a71</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62476f1563149</t>
+          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Data Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084df75f91ec6d79</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86ab352d5623702</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 2- PostgreSQL and Oracle</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11b446ceb41e959</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
+          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>United Data Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,137 +1546,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eaec25ac9a4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd750283bd66a194</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439edd18837f2621</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
@@ -1838,20 +1838,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,119 +1861,119 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>United Data Technologies</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6578712d22b37aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,85 +1983,85 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70fa931bf1e55748</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering Architect</t>
+          <t>Back-End Java Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1812a5b73a77a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Junior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>BlueVoyant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Data Modeling, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
+          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ops Solution Developer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,637 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Credit Karma</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d65770eee70d38</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Data Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Shelter Insurance</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d75f91a30326a4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Henderson Brothers Inc.</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>API Security Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdefea95134fef</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Concord Music Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Global Partners LP</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>API Security Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Hadoop, Hive, Spark, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eab8b2d540dc7593</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>API Developer - Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior QA Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8f4b98e26bdff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Back-End Java Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>BRMi</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Junior Dev Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>BlueVoyant</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
         </is>
       </c>
     </row>
